--- a/TomaInventarioWEB/Plantillas/Plantilla_Producto_Costos.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Producto_Costos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmspe\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F704D2-B874-4C76-86F8-ECFB2B89C8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E56416-F049-47A9-90B4-19A0BFB6D37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,52 +19,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Sistema</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{BB6DBF37-99F7-4C23-836F-E4E77637E44C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Complete con el código de un producto YA EXISTENTE en el sistema. No agregue filas ni columnas nuevas.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Esta es una fila de EJEMPLO. Bórrela antes de importar su archivo real.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Cod_Moneda (ref.)</t>
-  </si>
-  <si>
-    <t>Descripción</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>PROD001</t>
   </si>
@@ -79,6 +35,15 @@
   </si>
   <si>
     <t>COD_MONEDA</t>
+  </si>
+  <si>
+    <t>CÓDIGO</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN</t>
+  </si>
+  <si>
+    <t>LISTA DE TIPOS DE MONEDA (REFERENCIAL)</t>
   </si>
 </sst>
 </file>
@@ -95,8 +60,16 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -104,18 +77,12 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,20 +91,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5D87FF"/>
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor rgb="FF5D87FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFFFD966"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,17 +111,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB7B7B7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -168,20 +123,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFD966"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -477,48 +462,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" style="11" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="6" max="6" width="29.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="H2" s="5"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4">
-        <v>18.5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>